--- a/mapping/npc_giftcommitment_from_rd.xlsx
+++ b/mapping/npc_giftcommitment_from_rd.xlsx
@@ -443,6 +443,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -596,7 +597,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Exact name match (normalized). Only 100.0% populated, and every populated row has the same value ("005fj00000J30tNAAR") -- no differentiating information, likely not worth migrating.</t>
+          <t>Exact name match (normalized). Only 100.0% populated, and every populated row has the same value ("&lt;SAMPLE_ID_REDACTED&gt;") -- no differentiating information, likely not worth migrating.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -776,7 +777,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>No confident match found -- needs manual review. Also: Only 100.0% populated, and every populated row has the same value ("005fj00000J30tNAAR") -- no differentiating information, likely not worth migrating.</t>
+          <t>No confident match found -- needs manual review. Also: Only 100.0% populated, and every populated row has the same value ("&lt;SAMPLE_ID_REDACTED&gt;") -- no differentiating information, likely not worth migrating.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -846,7 +847,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>No confident match found -- needs manual review. Also: Only 100.0% populated, and every populated row has the same value ("005fj00000J30tNAAR") -- no differentiating information, likely not worth migrating.</t>
+          <t>No confident match found -- needs manual review. Also: Only 100.0% populated, and every populated row has the same value ("&lt;SAMPLE_ID_REDACTED&gt;") -- no differentiating information, likely not worth migrating.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
